--- a/Python/results/differences/average_percentage_changes.xlsx
+++ b/Python/results/differences/average_percentage_changes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,11 +466,6 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>averageLatency</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>95PercentileLatency</t>
         </is>
       </c>
@@ -500,9 +495,6 @@
         <v>3.464491470797389</v>
       </c>
       <c r="H2" t="n">
-        <v>19.25760514373049</v>
-      </c>
-      <c r="I2" t="n">
         <v>34.61411902777204</v>
       </c>
     </row>
@@ -531,9 +523,6 @@
         <v>-2.062055109569665</v>
       </c>
       <c r="H3" t="n">
-        <v>-36.47990951320478</v>
-      </c>
-      <c r="I3" t="n">
         <v>-33.00511542824852</v>
       </c>
     </row>
@@ -562,9 +551,6 @@
         <v>-0.5131671091557166</v>
       </c>
       <c r="H4" t="n">
-        <v>189.8536008621596</v>
-      </c>
-      <c r="I4" t="n">
         <v>243.2063508647544</v>
       </c>
     </row>
@@ -593,9 +579,6 @@
         <v>4.679364791288624</v>
       </c>
       <c r="H5" t="n">
-        <v>-15.78295780597526</v>
-      </c>
-      <c r="I5" t="n">
         <v>-11.72793251431497</v>
       </c>
     </row>
@@ -606,28 +589,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>730.2516819816146</v>
+        <v>1.152277562392631</v>
       </c>
       <c r="C6" t="n">
-        <v>1848.152107842338</v>
+        <v>1.84279285893552</v>
       </c>
       <c r="D6" t="n">
-        <v>4503.390572810031</v>
+        <v>1.267184784784992</v>
       </c>
       <c r="E6" t="n">
-        <v>2230.596410866341</v>
+        <v>2.199797030736017</v>
       </c>
       <c r="F6" t="n">
-        <v>25.051284274659</v>
+        <v>-8.658844491264992</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9325777700789596</v>
+        <v>-2.260829920695713</v>
       </c>
       <c r="H6" t="n">
-        <v>25.051284274659</v>
-      </c>
-      <c r="I6" t="n">
-        <v>29.04038052644864</v>
+        <v>-12.65163737366761</v>
       </c>
     </row>
   </sheetData>
